--- a/deliverables/05_Epic_UserStory.xlsx
+++ b/deliverables/05_Epic_UserStory.xlsx
@@ -2087,7 +2087,7 @@
     <t>Tách thành đổi mật khẩu (Must) và thông tin cá nhân (Should). Các trường thông tin vẫn cần xác nhận.</t>
   </si>
   <si>
-    <t>Cho phép thêm hộ gia đình mới gồm số căn hộ, chủ hộ, diện tích căn hộ (m²), thông tin liên hệ; không cho trùng số căn hộ.</t>
+    <t xml:space="preserve">BQT muốn lưu thông tin hộ gia đình tập trung và tránh trường hợp nhập trùng căn hộ.</t>
   </si>
   <si>
     <t>Việc nhập dữ liệu ban đầu từ Excel nằm ngoài phạm vi dự án (AS-08, C-08, OQ-12).</t>
@@ -2108,19 +2108,19 @@
     <t>Chồng lấn một phần với RAW-007. Ranh giới: RAW-005 ở cấp hộ (chủ hộ, hộ chuyển đi); RAW-007 là biến động ở cấp nhân khẩu.</t>
   </si>
   <si>
-    <t>Cho phép thêm, sửa nhân khẩu trong hộ: họ tên, ngày sinh, giới tính, quan hệ với chủ hộ, giấy tờ tùy thân (nếu có); không xóa cứng nhân khẩu đã rời đi.</t>
+    <t xml:space="preserve">BQT muốn quản lý thông tin những người thuộc từng hộ và vẫn tra cứu được người đã rời đi.</t>
   </si>
   <si>
     <t>Số giấy tờ tùy thân là tùy chọn (OQ-08); các trường nhân khẩu theo AS-18.</t>
   </si>
   <si>
-    <t>Ghi nhận biến động nhân khẩu (chuyển đến, chuyển đi, sinh, mất…) kèm ngày và lý do; xem lịch sử biến động của từng hộ và từng nhân khẩu.</t>
+    <t xml:space="preserve">BQT muốn theo dõi các thay đổi nhân khẩu của từng hộ theo thời gian.</t>
   </si>
   <si>
     <t>OQ-13: danh sách các loại biến động và thời hạn cập nhật. Story dùng chuyển đến, chuyển đi, sinh, mất làm danh sách đề xuất.</t>
   </si>
   <si>
-    <t>Ghi nhận tạm trú và tạm vắng của nhân khẩu với thời gian bắt đầu, kết thúc và lý do; đánh dấu khi hết thời hạn.</t>
+    <t xml:space="preserve">BQT muốn theo dõi tình trạng tạm trú/tạm vắng và thời hạn liên quan.</t>
   </si>
   <si>
     <t>Chỉ có giai đoạn và cờ hết hạn; các biểu mẫu pháp lý nằm ngoài phạm vi (OQ-07).</t>
@@ -2132,13 +2132,13 @@
     <t>OQ-07: các trường và biểu mẫu chính xác mà cơ quan chức năng yêu cầu. Việc đóng dấu chính thức nằm ngoài hệ thống (AS-16).</t>
   </si>
   <si>
-    <t>Cho phép tạo, xem, sửa, ngừng áp dụng khoản thu (phí dịch vụ, phí quản lý, khoản đóng góp) gồm tên, loại (bắt buộc / tự nguyện), kỳ thu hoặc đợt, đơn giá hoặc mức thu, hạn nộp; đơn giá cấu hình được.</t>
+    <t xml:space="preserve">BQT muốn tự quản lý các khoản thu và có thể thay đổi mức thu khi cần.</t>
   </si>
   <si>
     <t>Tách thành tạo, cập nhật/ngừng áp dụng và liệt kê. Miễn giảm và đơn giá riêng cho kiot hoặc penthouse không thuộc v1.0 (AS-14, OQ-02, OQ-03).</t>
   </si>
   <si>
-    <t>Hệ thống lập danh sách khoản phải thu của từng hộ theo kỳ và tự tính phí dịch vụ, phí quản lý theo diện tích × đơn giá; hiển thị rõ cách tính.</t>
+    <t xml:space="preserve">BQT muốn hệ thống hỗ trợ tính phí theo diện tích căn hộ để giảm tính toán thủ công.</t>
   </si>
   <si>
     <t>OQ-02 (miễn giảm), OQ-03 (đơn giá kiot và penthouse) và quy tắc làm tròn VND còn bỏ ngỏ. Tách thành sinh khoản phải thu và chi tiết cách tính. Việc in thông báo từ hệ thống không bắt buộc (AS-07, OQ-06).</t>
@@ -2150,7 +2150,7 @@
     <t>Khoản thu tự nguyện không bao giờ là nợ (AS-19). Mâu thuẫn với yêu cầu của cơ quan chức năng về danh sách người đóng góp được xử lý bằng cách chỉ báo cáo những người đã đóng góp (C-07).</t>
   </si>
   <si>
-    <t>Cho phép ghi nhận hộ nộp tiền: chọn hộ, khoản thu, số tiền, ngày nộp, hình thức nộp, người thu; hỗ trợ nộp một phần và nộp gộp nhiều khoản hoặc nhiều kỳ trong một lần.</t>
+    <t xml:space="preserve">Thủ quỹ muốn ghi nhận việc hộ nộp tiền, kể cả khi chỉ nộp một phần hoặc nhiều khoản cùng lúc.</t>
   </si>
   <si>
     <t>OQ-05 (phí trễ hạn, nộp trước, nộp thừa) và OQ-09 (hình thức thanh toán). Tách thành thanh toán đủ, một phần và gộp. Người nộp thay chỉ là ghi chú (AS-15).</t>
@@ -2162,13 +2162,13 @@
     <t>Đề bài không nêu (giả định). Bố cục biên lai là OQ-06.</t>
   </si>
   <si>
-    <t>Cho phép sửa hoặc hủy giao dịch thu nhầm kèm lý do; không xóa cứng, lưu người thực hiện và thời điểm.</t>
+    <t xml:space="preserve">Thủ quỹ muốn xử lý được giao dịch thu ghi nhầm; phần truy vết thay đổi nằm ở RAW-025 và NFR-004.</t>
   </si>
   <si>
     <t>OQ-14: tính lại sau khi sửa hoặc hủy. Không xóa cứng (AS-17).</t>
   </si>
   <si>
-    <t>Tìm hộ gia đình theo số căn hộ và tên chủ hộ; kết quả hiển thị nhanh kèm số tiền phải nộp.</t>
+    <t xml:space="preserve">Thủ quỹ và BQT muốn tìm hộ gia đình theo số căn hộ và tên chủ hộ, kèm số tiền phải nộp; yêu cầu tốc độ nằm ở NFR-006.</t>
   </si>
   <si>
     <t>Chồng lấn với RAW-018. Ranh giới: RAW-016 tìm một hộ và hiển thị tổng số còn nợ; RAW-018 hiển thị chi tiết khoản thu, lịch sử và bộ lọc.</t>
@@ -2186,7 +2186,7 @@
     <t>US-28</t>
   </si>
   <si>
-    <t>Tra cứu, lọc khoản thu và giao dịch theo hộ, khoản thu, kỳ, trạng thái nộp (đã nộp, còn thiếu, chưa nộp) và khoảng thời gian; xem công nợ và lịch sử nộp của một hộ.</t>
+    <t xml:space="preserve">BQT và Thủ quỹ muốn tra cứu khoản thu và lịch sử đóng tiền của từng hộ theo nhiều tiêu chí.</t>
   </si>
   <si>
     <t>Chồng lấn với RAW-016 và RAW-020. Ranh giới: RAW-018 là chi tiết theo từng hộ và bộ lọc chung; RAW-020 là danh sách các hộ chưa đóng để nhắc nợ.</t>
@@ -2222,7 +2222,7 @@
     <t>NFR</t>
   </si>
   <si>
-    <t>Xác thực an toàn: mật khẩu không lưu ở dạng rõ (băm), giới hạn số lần đăng nhập sai liên tiếp.</t>
+    <t xml:space="preserve">BQT muốn tài khoản được bảo vệ an toàn và hạn chế truy cập trái phép.</t>
   </si>
   <si>
     <t>NFR được hiện thực hóa thành Technical Story US-02; giới hạn khóa N và thời gian khóa là đề xuất hoặc chưa chốt.</t>
@@ -2231,7 +2231,7 @@
     <t>US-02</t>
   </si>
   <si>
-    <t>Phân quyền theo vai trò: tối thiểu phân biệt quản trị và người thu phí; chỉ quản trị được sửa hộ, nhân khẩu, khoản thu, đơn giá và tài khoản.</t>
+    <t xml:space="preserve">Mỗi loại người dùng chỉ được thực hiện công việc phù hợp với trách nhiệm của mình.</t>
   </si>
   <si>
     <t>OQ-04 và C-01: danh sách vai trò và ma trận vai trò – chức năng chưa được xác nhận. Story giả định mỗi người một tài khoản (AS-11). Việc quản trị viên quản lý tài khoản do US-41 đảm nhiệm.</t>
@@ -2243,25 +2243,25 @@
     <t>US-05, US-41</t>
   </si>
   <si>
-    <t>Bảo vệ dữ liệu cá nhân: che bớt số giấy tờ khi hiển thị thường ngày; chỉ tài khoản có quyền mới xem đầy đủ và xuất dữ liệu.</t>
+    <t xml:space="preserve">Thông tin cá nhân nhạy cảm chỉ được người có thẩm quyền xem.</t>
   </si>
   <si>
     <t>OQ-08 và C-03: có lưu số giấy tờ hay không, mức che và ai được xem. Được hiện thực hóa thành Technical Story.</t>
   </si>
   <si>
-    <t>Audit log: ghi người thực hiện, thời điểm, loại thao tác, giá trị trước và sau cho việc thêm, sửa, hủy dữ liệu thu phí và nhân khẩu, và mỗi lần xuất dữ liệu; log không sửa hoặc xóa được qua giao diện.</t>
+    <t xml:space="preserve">BQT muốn biết ai đã thay đổi dữ liệu quan trọng và thay đổi khi nào.</t>
   </si>
   <si>
     <t>Được hiện thực hóa thành một Technical Story (ghi nhật ký) và một story Could (xem nhật ký). Thời gian lưu giữ còn bỏ ngỏ (OQ-11).</t>
   </si>
   <si>
-    <t>Sao lưu và khôi phục dữ liệu: sao lưu tự động hoặc bằng một thao tác, có thể khôi phục khi cần.</t>
+    <t xml:space="preserve">BQT lo mất dữ liệu và muốn có cách sao lưu, khôi phục khi có sự cố.</t>
   </si>
   <si>
     <t>Được hiện thực hóa thành một Technical Story; tần suất mặc định hằng ngày là giả định; RTO chưa chốt.</t>
   </si>
   <si>
-    <t>Hiệu năng: tìm kiếm và hiển thị danh sách trong tối đa 3 giây với quy mô vài trăm hộ, vài nghìn nhân khẩu và 2–3 người dùng đồng thời.</t>
+    <t xml:space="preserve">Thủ quỹ muốn việc tìm kiếm và mở danh sách không bị chậm khi dữ liệu tăng.</t>
   </si>
   <si>
     <t>Technical Story với mục tiêu 3 giây và tải demo đề xuất (AS-13, OQ-10); là mục Definition of Done xuyên suốt ở các phase sau.</t>
@@ -2270,7 +2270,7 @@
     <t>US-39</t>
   </si>
   <si>
-    <t>Dễ dùng: giao diện tiếng Việt, tiền tệ VND hiển thị dễ đọc, thông báo lỗi rõ ràng; ghi nhận một lần nộp tiền không quá khoảng 5 thao tác chính; người không chuyên IT dùng được sau hướng dẫn ngắn.</t>
+    <t xml:space="preserve">Người dùng muốn giao diện tiếng Việt, dễ hiểu và thao tác thu phí đơn giản.</t>
   </si>
   <si>
     <t>Technical Story và là tiêu chí chấp nhận của story ghi nhận thanh toán; mục tiêu 5 bước là đề xuất.</t>
@@ -2392,78 +2392,78 @@
       <color theme="1" tint="0.3499862666707358"/>
       <family val="2"/>
       <sz val="22"/>
-      <name val="Century Gothic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <i/>
       <color rgb="FF595959"/>
       <sz val="9"/>
-      <name val="Century Gothic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <color theme="1"/>
       <family val="2"/>
       <sz val="11"/>
-      <name val="Century Gothic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <name val="Century Gothic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF404040"/>
       <sz val="9"/>
-      <name val="Century Gothic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC55A11"/>
       <sz val="9"/>
-      <name val="Century Gothic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FFBF9000"/>
       <sz val="9"/>
-      <name val="Century Gothic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FF548235"/>
       <sz val="9"/>
-      <name val="Century Gothic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <color theme="1" tint="0.3499862666707358"/>
       <family val="2"/>
       <sz val="22"/>
-      <name val="Century Gothic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FF404040"/>
       <sz val="9"/>
-      <name val="Century Gothic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="9"/>
-      <name val="Century Gothic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FF404040"/>
       <sz val="11"/>
-      <name val="Century Gothic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FF7F7F7F"/>
       <sz val="9"/>
-      <name val="Century Gothic"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="10">

--- a/deliverables/05_Epic_UserStory.xlsx
+++ b/deliverables/05_Epic_UserStory.xlsx
@@ -1599,7 +1599,7 @@
     <t>ROADMAP v2.0</t>
   </si>
   <si>
-    <t>Phí gửi xe và thu hộ điện, nước, internet: Roadmap / Future Release, Won't-have cho phiên bản hiện tại. Không viết story.</t>
+    <t>Phí gửi xe và thu hộ điện, nước, internet: Roadmap / Future Release, Không sử dụng cho phiên bản hiện tại. Không viết story.</t>
   </si>
   <si>
     <t>Epics — BlueMoon v1.0</t>
@@ -2288,7 +2288,7 @@
     <t>ROADMAP</t>
   </si>
   <si>
-    <t>Won't-have cho v1.0. Không tạo Epic, Feature hay User Story. Mức phí ô tô trong đề bài cần xác nhận.</t>
+    <t>Không sử dụng cho v1.0. Không tạo Epic, Feature hay User Story. Mức phí ô tô trong đề bài cần xác nhận.</t>
   </si>
   <si>
     <t>—</t>
@@ -2306,7 +2306,7 @@
     <t>[Roadmap v2.0] Quản lý các khoản thu hộ điện, nước, internet theo thông báo của nhà cung cấp dịch vụ.</t>
   </si>
   <si>
-    <t>Won't-have cho v1.0. Không tạo Epic, Feature hay User Story.</t>
+    <t>Không sử dụng cho v1.0. Không tạo Epic, Feature hay User Story.</t>
   </si>
   <si>
     <t>Các mục được rà soát ngoài danh sách RAW (không có RAW; không chuyển thành story)</t>
